--- a/Flipkart/Flipkart.xlsx
+++ b/Flipkart/Flipkart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc14a74c4011e7bf/Desktop/INTERNSHIP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc14a74c4011e7bf/Desktop/INTERNSHIP/Flipkart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{407B77E0-1328-42BD-851D-786E66B6B105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{407B77E0-1328-42BD-851D-786E66B6B105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BC315DC-9204-4188-AD22-8F211463241B}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="924" windowWidth="22860" windowHeight="12036" xr2:uid="{FD03CFCA-FB33-4CD7-A0DE-F4739C7EC45E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD03CFCA-FB33-4CD7-A0DE-F4739C7EC45E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="158">
   <si>
-    <t>Sr.no</t>
-  </si>
-  <si>
     <t>Test Scenarios</t>
   </si>
   <si>
@@ -499,6 +496,9 @@
   </si>
   <si>
     <t>Search icon should not enable</t>
+  </si>
+  <si>
+    <t>Sr.no(Test_case ID)</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1310,7 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{45E60F70-AEDA-469A-A473-522A448648B2}" name="Sr.no" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{45E60F70-AEDA-469A-A473-522A448648B2}" name="Sr.no(Test_case ID)" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DDDF6CAD-0E06-408F-8E53-DDBA5B334B54}" name="Test Scenarios" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{C3CDBE39-CDA6-4F06-9474-0733A7375B2A}" name="action" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{54E5706A-006B-4AF5-8340-B218AC828039}" name="Input " dataDxfId="3"/>
@@ -1631,27 +1631,27 @@
     <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1659,141 +1659,141 @@
         <v>1</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="D12" s="1">
         <v>8796321212</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="1">
         <v>87963212</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1">
         <v>87963212121</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="G17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1801,175 +1801,175 @@
         <v>2</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D21" s="1">
         <v>8796321212</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1">
         <v>87963212</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" s="1">
         <v>87963212121</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="G25" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="G27" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="G30" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1977,56 +1977,56 @@
         <v>3</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C33" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C34" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -2034,141 +2034,141 @@
         <v>4</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="G36" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="G37" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C38" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="G38" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="G39" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="G40" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="G41" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C43" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="G43" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="72" x14ac:dyDescent="0.3">
@@ -2176,56 +2176,56 @@
         <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="G44" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C45" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="G45" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="G46" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -2233,361 +2233,361 @@
         <v>6</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="49" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C49" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="G49" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="G50" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="3:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C51" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="3:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="53" spans="3:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C53" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="G53" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C54" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C55" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="G55" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="3:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C56" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C57" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="F57" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C58" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C59" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="E59" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="F60" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C61" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D61" s="1">
         <v>123</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C62" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D62" s="1">
         <v>12</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C63" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="3:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C65" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="3:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C66" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="3:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C67" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F67" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="G67" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="3:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="F68" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="G68" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
